--- a/data/trans_dic/IP31KM16_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 31,42</t>
+          <t>0,78; 12,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,55</t>
+          <t>0,65; 11,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 22,26</t>
+          <t>1,39; 8,5</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 15,52</t>
+          <t>7,35; 18,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 18,77</t>
+          <t>7,02; 17,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,03</t>
+          <t>8,37; 16,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 17,1</t>
+          <t>1,08; 10,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,84</t>
+          <t>5,21; 17,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,58</t>
+          <t>3,78; 10,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 31,71</t>
+          <t>10,97; 53,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 58,63</t>
+          <t>14,01; 31,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 47,03</t>
+          <t>15,06; 37,94</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,93</t>
+          <t>1,55; 13,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,73</t>
+          <t>0,0; 12,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,46</t>
+          <t>1,78; 9,6</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,87</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,73; 11,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,91</t>
+          <t>0,99; 6,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,82; 29,62</t>
+          <t>17,93; 31,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,07; 30,01</t>
+          <t>16,48; 29,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,55; 28,09</t>
+          <t>19,41; 28,74</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,53; 17,28</t>
+          <t>5,5; 13,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,77</t>
+          <t>6,83; 16,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,53</t>
+          <t>7,4; 13,96</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,63; 16,39</t>
+          <t>10,31; 16,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,57</t>
+          <t>10,92; 15,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,43</t>
+          <t>11,13; 15,0</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>4368</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>798; 22432</t>
+          <t>470; 7645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>670; 8621</t>
+          <t>358; 6207</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2767; 32500</t>
+          <t>1597; 9794</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>25764</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4968; 19498</t>
+          <t>8448; 21522</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9811; 23727</t>
+          <t>6969; 17391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17543; 37884</t>
+          <t>17926; 35469</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>7783</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2774; 9497</t>
+          <t>618; 5827</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>712; 7007</t>
+          <t>2819; 9713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4685; 13920</t>
+          <t>4216; 11964</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>32498</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9202; 22093</t>
+          <t>7661; 37231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7987; 44187</t>
+          <t>9869; 22180</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23652; 68214</t>
+          <t>21128; 53218</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3533</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>615; 5399</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>589; 5182</t>
+          <t>0; 4586</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1160; 7090</t>
+          <t>1334; 7192</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>893</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2670</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>396; 5257</t>
+          <t>0; 3456</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>325; 5253</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>833; 6773</t>
+          <t>907; 6168</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>61869</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20805; 36639</t>
+          <t>25206; 43970</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26465; 46528</t>
+          <t>20079; 36032</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51713; 78293</t>
+          <t>50929; 75421</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>29724</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9691; 22229</t>
+          <t>8636; 21564</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9170; 21225</t>
+          <t>9425; 23030</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21822; 38274</t>
+          <t>21837; 41184</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>87588</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>69400; 107035</t>
+          <t>70780; 112471</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>76109; 130845</t>
+          <t>67528; 96009</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>154711; 215729</t>
+          <t>145236; 195757</t>
         </is>
       </c>
     </row>
